--- a/Data/EXCEL/Transfer/salemon/20240711/4803-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/4803-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F29C5D5A-166D-424C-BE2B-B648689E05AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BB43F19-DBC1-4A7C-BA2B-C70125778170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{45FF444A-E0B7-4781-8EAC-2D7AE65607B0}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{039E2654-2FF0-4C33-BD64-7CC197AA3293}"/>
   </bookViews>
   <sheets>
     <sheet name="4803-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,16 +1261,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA18187B-F287-4ED9-802F-64424865B395}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506AA689-5C43-41E9-B81F-7EE3F58EC649}">
   <dimension ref="A1:Q161"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1297,7 +1297,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1379,7 +1379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1418,7 +1418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>44593</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>-37.200000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>44562</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>-32.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>44531</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>-13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>44501</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>44470</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>-9.01</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>44440</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>-9.16</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>44409</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>-9.58</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>44378</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>-9.8699999999999992</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>44348</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>-7.34</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>44317</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>-7.64</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>44287</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>-8.2100000000000009</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>44256</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>44228</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>-14.9</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>44197</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>-15.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>44166</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>-42.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44136</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>-42.4</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44105</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>-42.3</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44075</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>-41.6</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44044</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>-41.8</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44013</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>-41.5</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>43983</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>-40.9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>43952</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>-39.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>43922</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>43891</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>-34.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>43862</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>-20.5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>43831</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>-9.14</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>43800</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>43770</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>43739</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>43709</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>43678</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>43647</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>43617</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>43586</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>43556</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>43525</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>43497</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>43466</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>43435</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>43405</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>43374</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>43344</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>43313</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>43282</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>43252</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>43221</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>43191</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>43160</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43132</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>43101</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43070</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>43040</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43009</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>42979</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>42948</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>42917</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>42887</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>42856</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>42826</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>42795</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>42767</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>42736</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>42705</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>42675</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>42644</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>42614</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>42583</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>42552</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>42522</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>42491</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>42461</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>75.099999999999994</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>42430</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>42401</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>69.599999999999994</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>42370</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>108.9</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>42339</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>42309</v>
       </c>
@@ -5446,407 +5446,407 @@
         <v>39.299999999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>44075</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>43344</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>43282</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>43221</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="9">
         <v>43160</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>43101</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>43040</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>42979</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>42917</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>42856</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>42795</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>42736</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>42675</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>42614</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>42552</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>42491</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>42430</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>42370</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="9">
         <v>42309</v>
       </c>
